--- a/data_extactor/batch_10_fa/batch_0008_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0008_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Regulatory Affairs Specialists (متخصصان امور نظارتی)</t>
+          <t>متخصصان امور نظارتی (Regulatory Affairs Specialists)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Drug Regulatory Affairs Specialist | Regulatory Affairs Analyst (RA Analyst) | Regulatory Affairs Associate (RA Associate) | Regulatory Affairs Consultant (RA Consultant) | Regulatory Affairs Specialist (RA Specialist) | Regulatory Affairs Strategist (RA Strategist) | Regulatory Engineer | Regulatory Services Consultant | Regulatory Specialist | Regulatory Submissions Associate</t>
+          <t>کارشناس امور نظارتی دارو | تحلیل‌گر امور نظارتی (RA) | کارشناس امور نظارتی (RA) | مشاور امور نظارتی (RA) | کارشناس امور نظارتی (RA) | راهبردپرداز امور نظارتی (RA) | مهندس امور نظارتی | مشاور خدمات نظارتی | کارشناس امور نظارتی | کارشناس ارائه اسناد نظارتی</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Analyse-it | Atrion Intelligent Authoring | DataVision | FileMaker Pro | نرم‌افزار حسابداری صندوق | Healthcare common procedure coding system HCPCS | نرم‌افزار مدیریت منابع انسانی HRMS | نرم‌افزار محیط توسعه یکپارچه IDE | LexisNexis | McAfee | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | Qlik Tech QlikView | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار SAP | نرم‌افزار آماری | Structured query language SQL | نرم‌افزار مالیاتی | نرم‌افزار مرورگر وب | Yardi software</t>
+          <t>Adobe Acrobat | Analyse-it | Atrion Intelligent Authoring | DataVision | FileMaker Pro | نرم‌افزار حسابداری صندوق | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار مدیریت منابع انسانی HRMS | نرم‌افزار محیط توسعه یکپارچه IDE | LexisNexis | McAfee | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | Qlik Tech QlikView | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار SAP | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مالیاتی | نرم‌افزار مرورگر وب | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Speaking | Writing | Active Listening | Reading Comprehension | Critical Thinking | Monitoring | Active Learning | Learning Strategies</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>English Language | Law and Government | Biology | Computers and Electronics | Administration and Management | Administrative</t>
+          <t>زبان انگلیسی | قانون و دولت | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Written Comprehension | Written Expression | Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Speech Clarity | Speech Recognition | Information Ordering | Near Vision | Fluency of Ideas | Category Flexibility | Mathematical Reasoning</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-Mail | Spend Time Sitting | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Contact With Others | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Time Pressure | Written Letters and Memos | Coordinate or Lead Others in Accomplishing Work Activities</t>
+          <t>ایمیل | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Clinical Data Managers | Clinical Research Coordinators | Compliance Managers | Compliance Officers | Coroners | Customs Brokers | Document Management Specialists | Environmental Compliance Inspectors | Environmental Scientists and Specialists, Including Health | Equal Opportunity Representatives and Officers | Financial Risk Specialists | Government Property Inspectors and Investigators | Health Information Technologists and Medical Registrars | Information Security Engineers | Management Analysts | Medical Records Specialists | Project Management Specialists | Quality Control Analysts | Quality Control Systems Managers | Regulatory Affairs Managers</t>
+          <t>مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | مدیران انطباق | افسران انطباق | بازرسان مرگ | کارگزاران گمرک | متخصصان مدیریت اسناد | بازرسان انطباق زیست‌محیطی | دانشمندان و متخصصان محیط زیست، شامل بهداشت | نمایندگان و افسران فرصت‌های برابر | متخصصان ریسک مالی | بازرسان و محققان اموال دولتی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | متخصصان مدیریت پروژه | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | مدیران امور نظارتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Customs Brokers (کارگزاران گمرک)</t>
+          <t>کارگزاران گمرک (Customs Brokers)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Corporate Licensed Broker | Customs Broker</t>
+          <t>کارگزار دارای پروانه شرکتی | کارگزار گمرکی</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار محیط تجاری خودکار ACE | سیستم خودکار داده‌های گمرکی ASYCUDA | پایگاه‌های داده سوابق گمرکی | نرم‌افزار تبادل الکترونیکی داده‌ها EDI | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار نویسه‌خوان نوری OCR | پایگاه‌های داده طبقه‌بندی قطعات | SAP Customs Management | نرم‌افزار SAP | پایگاه‌های داده تعرفه | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار محیط تجاری خودکار ACE | سیستم خودکار داده‌های گمرکی ASYCUDA | پایگاه‌های داده سوابق گمرکی | نرم‌افزار تبادل الکترونیکی داده EDI | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار نویسه‌خوان نوری OCR | پایگاه‌های داده طبقه‌بندی قطعات | SAP Customs Management | نرم‌افزار SAP | پایگاه‌های داده تعرفه | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Active Listening | Reading Comprehension | Writing | Speaking | Critical Thinking | Monitoring | Active Learning | Learning Strategies | Mathematics</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Transportation | English Language | Administrative | Law and Government | Customer and Personal Service | Computers and Electronics | Administration and Management | Geography | Mathematics | Economics and Accounting</t>
+          <t>حمل و نقل | زبان انگلیسی | اداری | قانون و دولت | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | جغرافیا | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Written Comprehension | Deductive Reasoning | Near Vision | Oral Comprehension | Oral Expression | Written Expression | Speech Clarity | Information Ordering | Category Flexibility | Speech Recognition | Problem Sensitivity | Inductive Reasoning | Selective Attention | Flexibility of Closure | Fluency of Ideas</t>
+          <t>درک کتبی | استدلال قیاسی | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Spend Time Sitting | Importance of Being Exact or Accurate | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Repeating Same Tasks | Written Letters and Memos | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Level of Competition | Deal With External Customers or the Public in General | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Dealing With Unpleasant, Angry, or Discourteous People</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Brokerage Clerks | Buyers and Purchasing Agents, Farm Products | Cargo and Freight Agents | Compliance Officers | Customs and Border Protection Officers | Environmental Compliance Inspectors | Freight Forwarders | Government Property Inspectors and Investigators | Logisticians | Logistics Analysts | Postal Service Clerks | Procurement Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Regulatory Affairs Specialists | Securities, Commodities, and Financial Services Sales Agents | Shipping, Receiving, and Inventory Clerks | Transportation Inspectors | Transportation, Storage, and Distribution Managers | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>کارمندان کارگزاری | خریداران و نمایندگان خرید، محصولات کشاورزی | نمایندگان بار و محموله | افسران انطباق | ماموران گمرک و حفاظت مرزی | بازرسان انطباق زیست‌محیطی | متصدیان حمل و نقل | بازرسان و محققان اموال دولتی | لجستیسین‌ها | تحلیلگران لجستیک | کارمندان خدمات پستی | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | متخصصان امور نظارتی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان ارسال، دریافت و موجودی کالا | بازرسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cost Estimators (برآوردکنندگان هزینه)</t>
+          <t>برآوردکنندگان هزینه (Cost Estimators)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Acquisition Cost Estimator | Analyst | Construction Estimator | Cost Analyst | Cost Consultant | Cost Engineer | Cost Estimating Analyst | Cost Estimator | Estimating Specialist | Estimator</t>
+          <t>برآوردکننده هزینه تدارکات | تحلیل‌گر | برآوردکننده هزینه ساخت | تحلیل‌گر هزینه | مشاور هزینه | مهندس هزینه | تحلیل‌گر برآورد هزینه | برآوردکننده هزینه | کارشناس برآورد هزینه | برآوردکننده</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Apple AppleWorks | Assured Software JPP | Autodesk AutoCAD | Autodesk Revit | CPR International GeneralCOST Estimator | CPR Visual Estimator | Choice Job Cost | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | ConEst BidTrac | ConEst Electrical Formulas | ConEst IntelliBid Design Build | ConEst Intellibid | ConEst JobTrac | ConEst Permit Trac | ConEst SureCount | ConEst T&amp;M Billing Manager | ConstructConnect PlanSwift | Construction Management Software ProEst | Corel QuattroPro | نرم‌افزار حسابداری هزینه | نرم‌افزار برآورد هزینه | Dassault Systemes CATIA | Decisioneering Crystal Ball | EFI Hagen OA | Galorath SEER | Galorath SEER-SEM | HCSS HeavyBid | HCSS HeavyJob | IBM Costimater | IBM Lotus 1-2-3 | Intuit QuickBooks | Laserfiche Avante | Logic Software Easy Projects.NET | Microsoft Access | Microsoft Business Contact Manager | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Word | On Center On-Screen Takeoff | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PRICE Sytems TruePlanning | Palisade @Risk | Primavera Cost Management | Procore software | QSM SLIM Suite | Resources Calculations Incorporated SoftCost | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 100 Contractor | Sage 300 Construction and Real Estate | Sage 50 Accounting | Softstar Costar COCOMO II | نرم‌افزار سازمانی Software AG | Trimble SketchUp Pro | WinEstimator WinEst | Xactware Xactimate</t>
+          <t>Adobe Acrobat | Apple AppleWorks | Assured Software JPP | Autodesk AutoCAD | Autodesk Revit | CPR International GeneralCOST Estimator | CPR Visual Estimator | Choice Job Cost | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | ConEst BidTrac | ConEst Electrical Formulas | ConEst IntelliBid Design Build | ConEst Intellibid | ConEst JobTrac | ConEst Permit Trac | ConEst SureCount | ConEst T&amp;M Billing Manager | ConstructConnect PlanSwift | نرم‌افزار مدیریت ساخت ProEst | Corel QuattroPro | نرم‌افزار حسابداری هزینه | نرم‌افزار برآورد هزینه | Dassault Systemes CATIA | Decisioneering Crystal Ball | EFI Hagen OA | Galorath SEER | Galorath SEER-SEM | HCSS HeavyBid | HCSS HeavyJob | IBM Costimater | IBM Lotus 1-2-3 | Intuit QuickBooks | Laserfiche Avante | Logic Software Easy Projects.NET | Microsoft Access | Microsoft Business Contact Manager | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Word | On Center On-Screen Takeoff | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PRICE Sytems TruePlanning | Palisade @Risk | Primavera Cost Management | Procore software | QSM SLIM Suite | Resources Calculations Incorporated SoftCost | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 100 Contractor | Sage 300 Construction and Real Estate | Sage 50 Accounting | Softstar Costar COCOMO II | نرم‌افزار سازمانی Software AG | Trimble SketchUp Pro | WinEstimator WinEst | Xactware Xactimate</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Mathematics | Speaking | Active Listening | Critical Thinking | Writing | Active Learning | Monitoring</t>
+          <t>درک مطلب | ریاضیات | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathematics | Economics and Accounting | Computers and Electronics | Engineering and Technology | Building and Construction | English Language | Administration and Management | Design | Customer and Personal Service</t>
+          <t>ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک | مهندسی و فناوری | ساختمان و ساخت‌وساز | زبان انگلیسی | مدیریت و اداره | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inductive Reasoning | Mathematical Reasoning | Oral Comprehension | Oral Expression | Number Facility | Written Comprehension | Near Vision | Written Expression | Deductive Reasoning | Information Ordering | Speech Clarity | Speech Recognition | Category Flexibility | Problem Sensitivity | Selective Attention | Visualization | Flexibility of Closure | Fluency of Ideas</t>
+          <t>استدلال استقرایی | استدلال ریاضی | درک شفاهی | بیان شفاهی | توانایی عددی | درک کتبی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Time Pressure | Contact With Others</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Appraisers and Assessors of Real Estate | Architectural and Civil Drafters | Architectural and Engineering Managers | Civil Engineering Technologists and Technicians | Civil Engineers | Construction Managers | Construction and Building Inspectors | Electrical Engineers | Energy Auditors | Industrial Engineering Technologists and Technicians | Industrial Engineers | Logistics Engineers | Manufacturing Engineers | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Production, Planning, and Expediting Clerks | Project Management Specialists | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Sales Engineers | Solar Energy Installation Managers</t>
+          <t>ارزیابان و ممیزان املاک | نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | مهندسان برق | بازرسان انرژی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مهندسان فروش | مدیران نصب انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Resources Specialists (متخصصان منابع انسانی)</t>
+          <t>متخصصان منابع انسانی (Human Resources Specialists)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Corporate Recruiter | Employment Representative | HR Analyst (Human Resources Analyst) | HR Coordinator (Human Resources Coordinator) | HR Generalist (Human Resources Generalist) | Human Resources Representative (HR Rep) | Human Resources Specialist (HR Specialist) | Personnel Analyst | Personnel Officer | Recruiter</t>
+          <t>کارشناس جذب نیرو در شرکت | نماینده امور اشتغال | تحلیل‌گر منابع انسانی (HR) | هماهنگ‌کننده منابع انسانی (HR) | کارشناس عمومی منابع انسانی (HR) | نماینده منابع انسانی (HR Rep) | کارشناس منابع انسانی (HR Specialist) | تحلیل‌گر امور کارکنان | مسئول امور کارکنان | کارشناس جذب نیرو</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | AST Staff Matrix | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Human Capital Application Solution Accelerator | Adobe Illustrator | Adobe InDesign | Adobe LifeCycle Enterprise Suite | Adobe Photoshop | برنامه‌نویسی کاربردی تجاری پیشرفته ABAP | Airtable | Apple Final Cut Pro | Apple macOS | نرم‌افزار ردیابی متقاضیان | ApplicantPro iApplicants | Arbita OnePost | Arbita OneWorld | نرم‌افزار ارزیابی | نرم‌افزار بررسی سوابق | BlackDog Recruiting | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blackdog | Bond International Adapt Staffing | Bond International Software Bond StaffSuite | سیستم ردیابی متقاضیان BrightMove | Bullhorn Applicant Tracking System | COATSsql | CVTracer | نرم‌افزار غربالگری متقاضیان | نرم‌افزار ردیابی متقاضیان | Careerbuilder.com | Cisco Webex | Cluen Encore | نرم‌افزار استخدام اجرایی Cluen | DGCC.com RecruitTrack | Data Frenzy | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Drupal | نرم‌افزار ESRI ArcGIS | Ellucian Banner Human Resources | Enterprise JavaBeans | Evernote | زبان نشانه‌گذاری توسعه‌پذیر XML | FaceTime | Facebook | FileMaker Pro | GitHub | GoBackgrounds | Google | Google Ads | Google Analytics | Google Docs | Google Drive | Google Meet | Google Slides | HRM Direct | HireAbility ResumeParser | HireLogic PowerPlace | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری فرامتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار سیستم‌های قدرت IBM | IBM SPSS Statistics | ICIMS | Industrial Code Recruitpoint.net | Intelius | Intelligent Algorithms InfoGIST Platinum Recruiter | Intuit QuickBooks | نرم‌افزار ارسال آگهی شغلی | Kronos Workforce HR | Kronos Workforce Payroll | Kronos Workforce Timekeeper | Lawson Human Resource Management | LexisNexis | LinkedIn | Loom | نرم‌افزار MEDITECH | MPAY Millennium | Main Sequence Technologies PCRecruiter | Main Sequence Technologies PCRecruiter Resume Inhaler | Marketo Marketing Automation | Micro J Systems PcHunter | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | سرویس‌های گزارش‌دهی Microsoft SQL Server SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | NetSuite ERP | پایگاه‌های داده آنلاین | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle HRIS | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle PeopleSoft Human Capital Management | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | نرم‌افزار Perforce Helix | Post Once | PostingPal | PowerPlace Professional | Qlik Tech QlikView | Recruit Wizard | RecruitTrack | نرم‌افزار مدیریت استخدام | Recruitpoint.net | Resource Edge TalentHook Sphere | نرم‌افزار تبدیل رزومه | نرم‌افزار استخراج و جستجوی رزومه | نرم‌افزار پردازش رزومه | ResumeRobot | SAP Business Objects | SAP Crystal Reports | SAP ERP Human Capital Management | نرم‌افزار SAP | SAS | Safari Software Products Safari | Sage 50 Accounting | نرم‌افزار Salesforce | Sendouts Recruiting | Silk Road technology OpenHire | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Staffing Solutions Enterprises Staff Matrix | StaffingSoft Staffing Edition | StataCorp Stata | Tableau | Talent Technology HireDesk | Talent Technology Resume Mirror | Talent Technology Talemetry | TalentHook | نرم‌افزار مالیاتی | Technomedia Hodes iQ | نرم‌افزار استخدام و تأمین نیروی TempWorks | Teradata Database | VCG Pointwing | نرم‌افزار سیستم مدیریت فروشندگان | نرم‌افزار مرورگر وب | نرم‌افزار Workday | YouTube | Zoom | eQuest</t>
+          <t>ADP Workforce Now | AST Staff Matrix | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Human Capital Application Solution Accelerator | Adobe Illustrator | Adobe InDesign | Adobe LifeCycle Enterprise Suite | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Apple Final Cut Pro | Apple macOS | نرم‌افزار ردیابی متقاضی | ApplicantPro iApplicants | Arbita OnePost | Arbita OneWorld | نرم‌افزار ارزیابی | نرم‌افزار بررسی سوابق | BlackDog Recruiting | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blackdog | Bond International Adapt Staffing | Bond International Software Bond StaffSuite | سیستم ردیابی متقاضیان BrightMove | Bullhorn Applicant Tracking System | COATSsql | CVTracer | نرم‌افزار غربالگری متقاضیان | نرم‌افزار ردیابی متقاضیان | Careerbuilder.com | Cisco Webex | Cluen Encore | نرم‌افزار استخدام اجرایی Cluen | DGCC.com RecruitTrack | Data Frenzy | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Drupal | نرم‌افزار ESRI ArcGIS | Ellucian Banner Human Resources | Enterprise JavaBeans | Evernote | زبان نشانه‌گذاری توسعه‌پذیر XML | FaceTime | Facebook | FileMaker Pro | GitHub | GoBackgrounds | Google | Google Ads | Google Analytics | Google Docs | Google Drive | Google Meet | Google Slides | HRM Direct | HireAbility ResumeParser | HireLogic PowerPlace | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | ICIMS | Industrial Code Recruitpoint.net | Intelius | Intelligent Algorithms InfoGIST Platinum Recruiter | Intuit QuickBooks | نرم‌افزار ارسال آگهی شغلی | Kronos Workforce HR | Kronos Workforce Payroll | Kronos Workforce Timekeeper | Lawson Human Resource Management | LexisNexis | LinkedIn | Loom | نرم‌افزار MEDITECH | MPAY Millennium | Main Sequence Technologies PCRecruiter | Main Sequence Technologies PCRecruiter Resume Inhaler | Marketo Marketing Automation | Micro J Systems PcHunter | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | NetSuite ERP | پایگاه‌های داده آنلاین | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle HRIS | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle PeopleSoft Human Capital Management | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | نرم‌افزار Perforce Helix | Post Once | PostingPal | PowerPlace Professional | Qlik Tech QlikView | Recruit Wizard | RecruitTrack | نرم‌افزار مدیریت استخدام | Recruitpoint.net | Resource Edge TalentHook Sphere | نرم‌افزار تبدیل رزومه | نرم‌افزار استخراج و جستجوی رزومه | نرم‌افزار پردازش رزومه | ResumeRobot | SAP Business Objects | SAP Crystal Reports | SAP ERP Human Capital Management | نرم‌افزار SAP | SAS | Safari Software Products Safari | Sage 50 Accounting | نرم‌افزار Salesforce | Sendouts Recruiting | Silk Road technology OpenHire | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Staffing Solutions Enterprises Staff Matrix | StaffingSoft Staffing Edition | StataCorp Stata | Tableau | Talent Technology HireDesk | Talent Technology Resume Mirror | Talent Technology Talemetry | TalentHook | نرم‌افزار مالیاتی | Technomedia Hodes iQ | نرم‌افزار استخدام و تأمین نیروی TempWorks | Teradata Database | VCG Pointwing | نرم‌افزار سیستم مدیریت فروشندگان | نرم‌افزار مرورگر وب | نرم‌افزار Workday | YouTube | Zoom | eQuest</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Reading Comprehension | Writing | Critical Thinking | Active Learning | Monitoring | Learning Strategies</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Personnel and Human Resources | Administrative | Administration and Management | English Language | Customer and Personal Service | Law and Government | Education and Training</t>
+          <t>پرسنل و منابع انسانی | اداری | مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Speech Clarity | Near Vision | Inductive Reasoning | Information Ordering | Category Flexibility</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Contact With Others | Work With or Contribute to a Work Group or Team | Written Letters and Memos | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Spend Time Sitting | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Conflict Situations | Importance of Repeating Same Tasks | Time Pressure | Deal With External Customers or the Public in General | Work Outcomes and Results of Other Workers | Spend Time Making Repetitive Motions</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | اهمیت تکرار وظایف یکسان | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Administrative Services Managers | Compensation and Benefits Managers | Compensation, Benefits, and Job Analysis Specialists | Eligibility Interviewers, Government Programs | Equal Opportunity Representatives and Officers | Executive Secretaries and Executive Administrative Assistants | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Managers | Industrial-Organizational Psychologists | Labor Relations Specialists | Management Analysts | Payroll and Timekeeping Clerks | Project Management Specialists | Social and Community Service Managers | Training and Development Managers | Training and Development Specialists</t>
+          <t>مدیران خدمات اداری | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | روان‌شناسان صنعتی-سازمانی | متخصصان روابط کار | تحلیل‌گران مدیریت | کارمندان حقوق و دستمزد و ثبت زمان | متخصصان مدیریت پروژه | مدیران خدمات اجتماعی و جامعه | مدیران آموزش و توسعه | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Farm Labor Contractors (پیمانکاران نیروی کار کشاورزی)</t>
+          <t>پیمانکاران نیروی کار کشاورزی (Farm Labor Contractors)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Farm Labor Contractor | Field Manager | Field Supervisor</t>
+          <t>پیمانکار تأمین نیروی کار کشاورزی | مدیر میدانی | سرپرست میدانی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Speaking | Active Listening | Critical Thinking</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Foreign Language | Food Production | Mathematics | Personnel and Human Resources | Production and Processing | Law and Government</t>
+          <t>زبان خارجی | تولید مواد غذایی | ریاضیات | پرسنل و منابع انسانی | تولید و فرآوری | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Problem Sensitivity | Near Vision</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Repeating Same Tasks | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Sitting | Frequency of Decision Making | Level of Competition | Work With or Contribute to a Work Group or Team | Written Letters and Memos | Physical Proximity | Exposed to Contaminants</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Agricultural Inspectors | Buyers and Purchasing Agents, Farm Products | Construction Managers | Farm and Home Management Educators | Farmers, Ranchers, and Other Agricultural Managers | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | General and Operations Managers | Industrial Production Managers</t>
+          <t>بازرسان کشاورزی | خریداران و نمایندگان خرید، محصولات کشاورزی | مدیران ساخت‌وساز | مربیان مدیریت مزرعه و خانه | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیات | مدیران تولید صنعتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Labor Relations Specialists (متخصصان روابط کار)</t>
+          <t>متخصصان روابط کار (Labor Relations Specialists)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Business Agent | Business Representative | Grievance Manager | Labor Relations Specialist | Labor Specialist</t>
+          <t>نماینده امور تجاری | نماینده بازرگانی | مدیر رسیدگی به شکایات | کارشناس روابط کار | کارشناس امور کار</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Active Listening | Speaking | Critical Thinking | Writing | Reading Comprehension | Active Learning | Monitoring | Learning Strategies</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | درک مطلب | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Personnel and Human Resources | English Language | Law and Government | Administration and Management</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oral Expression | Oral Comprehension | Written Comprehension | Written Expression | Problem Sensitivity | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Speech Recognition | Near Vision | Originality | Fluency of Ideas | Information Ordering | Category Flexibility</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | اصالت | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Freedom to Make Decisions | Indoors, Environmentally Controlled | Spend Time Sitting | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Conflict Situations | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Written Letters and Memos | Time Pressure | Importance of Being Exact or Accurate | Dealing With Unpleasant, Angry, or Discourteous People</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | اهمیت دقیق یا درست بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Administrative Services Managers | Arbitrators, Mediators, and Conciliators | Chief Executives | Compensation and Benefits Managers | Compensation, Benefits, and Job Analysis Specialists | Compliance Managers | Eligibility Interviewers, Government Programs | Equal Opportunity Representatives and Officers | Executive Secretaries and Executive Administrative Assistants | First-Line Supervisors of Office and Administrative Support Workers | Human Resources Assistants, Except Payroll and Timekeeping | Human Resources Managers | Human Resources Specialists | Industrial-Organizational Psychologists | Lawyers | Management Analysts | Public Relations Managers | Public Relations Specialists | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Social and Community Service Managers</t>
+          <t>مدیران خدمات اداری | داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | متخصصان منابع انسانی | روان‌شناسان صنعتی-سازمانی | وکلا | تحلیل‌گران مدیریت | مدیران روابط عمومی | متخصصان روابط عمومی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Logisticians (لجستیسین‌ها)</t>
+          <t>لجستیسین‌ها (Logisticians)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Client Services Administrator | Logistician | Production Planner | Supply Management Specialist</t>
+          <t>مسئول خدمات مشتریان | متخصص لجستیک | برنامه‌ریز تولید | کارشناس مدیریت تأمین</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | IBM Cognos Impromptu | نرم‌افزار سیستم‌های قدرت IBM | Intuit QuickBooks | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle E-Business Suite | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار مدیریت سفارش | نرم‌افزار خرید | نرم‌افزار شناسایی فرکانس رادیویی RFID | RedPrairie E2e | نرم‌افزار SAP | SmugMug Flickr | Structured query language SQL | سیستم مدیریت انبار WMS | نرم‌افزار مرورگر وب</t>
+          <t>Autodesk AutoCAD | IBM Cognos Impromptu | نرم‌افزار IBM Power Systems | Intuit QuickBooks | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle E-Business Suite | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار مدیریت سفارش | نرم‌افزار خرید | نرم‌افزار شناسایی فرکانس رادیویی RFID | RedPrairie E2e | نرم‌افزار SAP | SmugMug Flickr | زبان پرس‌وجوی ساختاریافته SQL | سیستم مدیریت انبار WMS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Critical Thinking | Reading Comprehension | Active Listening | Speaking | Monitoring | Active Learning | Writing | Learning Strategies | Mathematics</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Transportation | English Language | Administration and Management | Customer and Personal Service | Mathematics | Computers and Electronics | Economics and Accounting | Public Safety and Security | Geography | Sales and Marketing | Production and Processing | Education and Training | Personnel and Human Resources | Law and Government</t>
+          <t>حمل و نقل | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | ایمنی و امنیت عمومی | جغرافیا | فروش و بازاریابی | تولید و فرآوری | آموزش و پرورش | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Information Ordering | Speech Recognition | Speech Clarity | Written Expression | Near Vision | Originality | Fluency of Ideas | Number Facility | Category Flexibility | Visualization | Flexibility of Closure | Mathematical Reasoning</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | اصالت | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Telephone Conversations | E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Written Letters and Memos | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Spend Time Sitting | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making</t>
+          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cargo and Freight Agents | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Non-Retail Sales Workers | General and Operations Managers | Industrial Production Managers | Information Technology Project Managers | Logistics Analysts | Logistics Engineers | Management Analysts | Procurement Clerks | Production, Planning, and Expediting Clerks | Project Management Specialists | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Recycling Coordinators | Sales Managers | Software Developers | Supply Chain Managers | Transportation, Storage, and Distribution Managers</t>
+          <t>نمایندگان بار و محموله | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | مدیران عمومی و عملیات | مدیران تولید صنعتی | مدیران پروژه فناوری اطلاعات | تحلیلگران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | هماهنگ‌کنندگان بازیافت | مدیران فروش | توسعه‌دهندگان نرم‌افزار | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Logistics Engineers (مهندسان لجستیک)</t>
+          <t>مهندسان لجستیک (Logistics Engineers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Acquisition Logistics Engineer | Logistics Engineer | Logistics Specialist | Reliability Engineer | Supportability Engineer | Systems Engineer</t>
+          <t>مهندس لجستیک تدارکات | مهندس لجستیک | کارشناس لجستیک | مهندس قابلیت اطمینان | مهندس پشتیبانی‌پذیری | مهندس سیستم‌ها</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار تحلیل حالات خرابی و اثرات آن FMEA | IBM Cognos Impromptu | IBM ILOG CPLEX Optimization Studio | IBM Notes | ITEM Software ITEM ToolKit | ITEM Software Spare Cost | JDA Manugistics | JMS Software RCM WorkSaver | LOGSA COMPASS | LOGSA SYSPARS | ابزار برآورد هزینه لجستیک | نرم‌افزار تحلیلگر پشتیبانی لجستیک SmartLogic | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | Oracle Database | Oracle Hyperion | Oracle Java | Oracle Primavera Enterprise Project Portfolio Management | Prolog | Python | Relex FMEA | ReliaSoft RCM++ | ReliaSoft XFMEA | نرم‌افزار نگهداری متمرکز بر قابلیت اطمینان RCM | Reliass EAGLE | SAP Business Objects | نرم‌افزار SAP | SAS | Structured query language SQL | Tableau | سیستم مدیریت انبار WMS | i2 Transportation Modeler</t>
+          <t>Autodesk AutoCAD | C++ | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار تحلیل حالات خرابی و اثرات آن FMEA | IBM Cognos Impromptu | IBM ILOG CPLEX Optimization Studio | IBM Notes | ITEM Software ITEM ToolKit | ITEM Software Spare Cost | JDA Manugistics | JMS Software RCM WorkSaver | LOGSA COMPASS | LOGSA SYSPARS | ابزار برآورد هزینه لجستیک | نرم‌افزار تحلیلگر پشتیبانی لجستیک SmartLogic | نرم‌افزار پایگاه داده اطلاعات مدیریت لجستیک LMI | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | Oracle Database | Oracle Hyperion | Oracle Java | Oracle Primavera Enterprise Project Portfolio Management | Prolog | Python | Relex FMEA | ReliaSoft RCM++ | ReliaSoft XFMEA | نرم‌افزار نگهداری متمرکز بر قابلیت اطمینان RCM | Reliass EAGLE | SAP Business Objects | نرم‌افزار SAP | SAS | زبان پرس‌وجوی ساختاریافته SQL | Tableau | سیستم مدیریت انبار WMS | i2 Transportation Modeler</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Writing | Active Learning | Active Listening | Reading Comprehension | Mathematics | Speaking | Critical Thinking | Monitoring | Learning Strategies</t>
+          <t>نگارش | یادگیری فعال | گوش دادن فعال | درک مطلب | ریاضیات | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Engineering and Technology | Mathematics | Transportation | Production and Processing | Computers and Electronics | English Language | Economics and Accounting | Administration and Management | Design | Education and Training | Customer and Personal Service</t>
+          <t>مهندسی و فناوری | ریاضیات | حمل و نقل | تولید و فرآوری | رایانه و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | مدیریت و اداره | طراحی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Written Comprehension | Mathematical Reasoning | Written Expression | Fluency of Ideas | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Information Ordering | Oral Comprehension | Oral Expression | Originality | Near Vision | Speech Clarity | Number Facility | Category Flexibility | Speech Recognition | Flexibility of Closure | Visualization | Far Vision | Selective Attention</t>
+          <t>درک کتبی | استدلال ریاضی | بیان کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | اصالت | بینایی نزدیک | وضوح گفتار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | انعطاف‌پذیری بستار | تجسم | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-Mail | Indoors, Environmentally Controlled | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Sitting | Time Pressure | Importance of Being Exact or Accurate | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Written Letters and Memos | Deal With External Customers or the Public in General</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | فشار زمانی | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Architectural and Engineering Managers | Automotive Engineers | Civil Engineering Technologists and Technicians | Computer Systems Engineers/Architects | Cost Estimators | Electronics Engineers, Except Computer | Industrial Engineering Technologists and Technicians | Industrial Engineers | Industrial Production Managers | Logisticians | Logistics Analysts | Manufacturing Engineers | Mechanical Engineering Technologists and Technicians | Mechatronics Engineers | Operations Research Analysts | Project Management Specialists | Sales Engineers | Software Developers | Supply Chain Managers | Transportation, Storage, and Distribution Managers</t>
+          <t>مدیران معماری و مهندسی | مهندسان خودرو | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان و معماران سامانه‌های رایانه‌ای | برآوردکنندگان هزینه | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | مهندسان فروش | توسعه‌دهندگان نرم‌افزار | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Logistics Analysts (تحلیلگران لجستیک)</t>
+          <t>تحلیلگران لجستیک (Logistics Analysts)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Global Logistics Analyst | Logistics Analyst | Logistics Management Analyst | Material Supply Planner | Supply Chain Analyst | Transportation Analyst</t>
+          <t>تحلیل‌گر لجستیک جهانی | تحلیل‌گر لجستیک | تحلیل‌گر مدیریت لجستیک | برنامه‌ریز تأمین مواد | تحلیل‌گر زنجیره تأمین | تحلیلگر حمل‌ونقل</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3PL Central | برنامه‌نویسی کاربردی تجاری پیشرفته ABAP | Amazon Redshift | سیستم توزیع لجستیک یکپارچه Cadre Technologies Accuplus | ESRI ArcLogistics | نرم‌افزار مدیریت ناوگان | نرم‌افزار نمودار جریان | Four Soft 4S VisiLog | Four Soft 4S eLog | نرم‌افزار گرافیکی | IBM Cognos Impromptu | IBM Notes | IBM SPSS Statistics | IntelliTrack 3PL | نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | Logisuite Enterprise | Logisuite Forwarder | MicroStrategy | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | Minitab | نرم‌افزار بهینه‌سازی | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle E-Business Suite Logistics | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Qlik Tech QlikView | نرم‌افزار گزارش‌دهی | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | StataCorp Stata | Structured query language SQL | Tableau | The MathWorks MATLAB | سیستم مدیریت انبار WMS</t>
+          <t>3PL Central | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon Redshift | Cadre Technologies Accuplus Integrated Distribution Logistics System | ESRI ArcLogistics | نرم‌افزار مدیریت ناوگان | نرم‌افزار نمودار جریان | Four Soft 4S VisiLog | Four Soft 4S eLog | نرم‌افزار گرافیکی | IBM Cognos Impromptu | IBM Notes | IBM SPSS Statistics | IntelliTrack 3PL | نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | Logisuite Enterprise | Logisuite Forwarder | MicroStrategy | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | Minitab | نرم‌افزار بهینه‌سازی | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle E-Business Suite Logistics | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Qlik Tech QlikView | نرم‌افزار گزارش‌دهی | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Critical Thinking | Reading Comprehension | Active Listening | Speaking | Monitoring | Writing | Active Learning | Mathematics</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>English Language | Computers and Electronics | Transportation | Mathematics | Administration and Management | Customer and Personal Service | Education and Training | Geography | Administrative | Production and Processing | Law and Government</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | حمل و نقل | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | جغرافیا | اداری | تولید و فرآوری | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Oral Expression | Written Comprehension | Near Vision | Speech Recognition | Information Ordering | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Mathematical Reasoning | Speech Clarity | Number Facility | Flexibility of Closure | Selective Attention | Category Flexibility | Written Expression | Originality | Fluency of Ideas | Perceptual Speed</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | وضوح گفتار | توانایی عددی | انعطاف‌پذیری بستار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | اصالت | روانی ایده‌ها | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Indoors, Environmentally Controlled | Contact With Others | Spend Time Sitting | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Freedom to Make Decisions | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Making Repetitive Motions</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Business Continuity Planners | Business Intelligence Analysts | Cargo and Freight Agents | Computer Systems Analysts | Data Warehousing Specialists | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | Freight Forwarders | Industrial Engineers | Industrial Production Managers | Logisticians | Logistics Engineers | Management Analysts | Procurement Clerks | Production, Planning, and Expediting Clerks | Project Management Specialists | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Shipping, Receiving, and Inventory Clerks | Supply Chain Managers | Transportation, Storage, and Distribution Managers</t>
+          <t>برنامه‌ریزان تداوم کسب‌وکار | تحلیلگران هوش تجاری | نمایندگان بار و محموله | تحلیلگران سیستم‌های کامپیوتری | متخصصان انبارش داده | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | متصدیان حمل و نقل | مهندسان صنایع | مدیران تولید صنعتی | لجستیسین‌ها | مهندسان لجستیک | تحلیل‌گران مدیریت | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | کارمندان ارسال، دریافت و موجودی کالا | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Project Management Specialists (متخصصان مدیریت پروژه)</t>
+          <t>متخصصان مدیریت پروژه (Project Management Specialists)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Program Coordinator | Project Administrator | Project Analyst | Project Controls Specialist | Project Coordinator | Project Lead | Project Management Specialist | Project Manager | Project Planner | Project Scheduler</t>
+          <t>هماهنگ‌کننده برنامه | مسئول امور پروژه | تحلیل‌گر پروژه | کارشناس کنترل پروژه | هماهنگ‌کننده پروژه | سرپرست پروژه | کارشناس مدیریت پروژه | مدیر پروژه | برنامه‌ریز پروژه | زمان‌بند پروژه</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Administration and Management | English Language | Customer and Personal Service | Computers and Electronics | Economics and Accounting | Mathematics | Personnel and Human Resources | Engineering and Technology | Education and Training</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | اقتصاد و حسابداری | ریاضیات | پرسنل و منابع انسانی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Administrative Services Managers | Architectural and Engineering Managers | Computer Systems Analysts | Computer Systems Engineers/Architects | Computer and Information Systems Managers | Construction Managers | First-Line Supervisors of Office and Administrative Support Workers | General and Operations Managers | Industrial Engineers | Information Technology Project Managers | Logisticians | Logistics Analysts | Logistics Engineers | Management Analysts | Natural Sciences Managers | Operations Research Analysts | Production, Planning, and Expediting Clerks | Software Developers | Solar Energy Installation Managers | Training and Development Managers</t>
+          <t>مدیران خدمات اداری | مدیران معماری و مهندسی | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران ساخت‌وساز | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران عمومی و عملیات | مهندسان صنایع | مدیران پروژه فناوری اطلاعات | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | مدیران علوم طبیعی | تحلیل‌گران تحقیق در عملیات | کارمندان تولید، برنامه‌ریزی و هماهنگی | توسعه‌دهندگان نرم‌افزار | مدیران نصب انرژی خورشیدی | مدیران آموزش و توسعه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0008_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0008_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | زیست‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | قانون و دولت | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | دید نزدیک | روانی کلام و ایده | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران داده‌های بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | مدیران انطباق با مقررات | کارشناسان انطباق با مقررات | پزشکان قانونی | ترخیص‌کاران و کارگزاران گمرکی | کارشناسان مدیریت اسناد و مدارک | بازرسان انطباق زیست‌محیطی | دانشمندان و متخصصان محیط زیست از جمله سلامت | نمایندگان و کارشناسان برابری فرصت‌های شغلی | کارشناسان ریسک مالی | بازرسان و ممیزان اموال دولتی | فناوران اطلاعات سلامت و ثبات‌های پزشکی | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت و فرایند | کارشناسان مدارک پزشکی | کارشناسان مدیریت پروژه | کارشناسان کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | مدیران امور رگولاتوری</t>
+          <t>مدیران داده‌های بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | حق‌العمل‌کاران و کارگزاران گمرکی | کارشناسان مدیریت اسناد و مدارک | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | کارشناسان ریسک مالی | بازرسان و ممیزان اموال دولتی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مهندسان امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان مدیریت پروژه | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | مدیران امور انطباق مقرراتی و حقوقی صنایع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حمل‌ونقل و ترابری | زبان انگلیسی | امور اداری و دفتری | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | جغرافیا | ریاضیات | اقتصاد و حسابداری</t>
+          <t>حمل و نقل | زبان انگلیسی | اداری | قانون و دولت | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | جغرافیا | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | دید نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری بستار | روانی کلام و ایده</t>
+          <t>درک کتبی | استدلال قیاسی | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | حساسیت به مسئله | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارمندان کارگزاری و ترخیص | خریداران و مأموران خرید محصولات کشاورزی | متصدیان بار و حمل‌ونقل کالا | کارشناسان انطباق با مقررات | مأموران گمرک و حفاظت مرزی | بازرسان انطباق زیست‌محیطی | متصدیان ارسال و خدمات فورواردری کالا | بازرسان و ممیزان اموال دولتی | کارشناسان لجستیک | تحلیل‌گران لجستیک | کارمندان خدمات پستی | کارمندان تدارکات و کارپردازی | مأموران خرید سایر حوزه‌ها | مدیران تدارکات و خرید | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان فروش اوراق، کالا و خدمات مالی | کارمندان انبارداری، دریافت و ارسال کالا | بازرسان حمل‌ونقل و ترابری | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده و خرد سایر حوزه‌ها</t>
+          <t>کارشناسان امور اداری و معاملات کارگزاری | خریداران و کارشناسان خرید محصولات کشاورزی | کارگزاران حمل‌ونقل و بار | کارشناسان پایش انطباق و بازرسی مقرراتی | ماموران گمرک و حفاظت مرزی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | بازرسان و ممیزان اموال دولتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | متصدیان باجه و امور پستی | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان انبار، ارسال و دریافت کالا | بازرسان ترابری و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | ریاضیات | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک | مهندسی و فناوری | ساختمان‌سازی و سازه | زبان انگلیسی | مدیریت و امور اداری | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک | مهندسی و فناوری | ساختمان و ساخت‌وساز | زبان انگلیسی | مدیریت و اداره | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال ریاضی | درک شفاهی | بیان شفاهی | مهارت کار با اعداد | درک کتبی | دید نزدیک | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | روانی کلام و ایده</t>
+          <t>استدلال استقرایی | استدلال ریاضی | درک شفاهی | بیان شفاهی | توانایی عددی | درک کتبی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان قیمت‌گذاری املاک | نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه ساختمانی و عمرانی | بازرسان ساختمان و سازه | مهندسان برق | ممیزان انرژی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید و ساخت | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارمندان برنامه‌ریزی تولید و تدارکات | کارشناسان مدیریت پروژه | مأموران خرید سایر حوزه‌ها | مهندسان فروش فنی | مدیران نصب تأسیسات انرژی خورشیدی</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | نقشه‌کشان معماری و عمران | مدیران فنی و مهندسی و معماری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | مهندسان برق | ممیزان انرژی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | کارشناسان خرید و امور قراردادها | مهندسان فروش | مدیران اجرای پروژه‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | امور اداری و دفتری | مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | آموزش و یادگیری</t>
+          <t>پرسنل و منابع انسانی | اداری | مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | مدیران حقوق، دستمزد و مزایا | کارشناسان حقوق، مزایا و طبقه‌بندی مشاغل | مصاحبه‌کنندگان و کارشناسان واجدین شرایط در برنامه‌های دولتی | نمایندگان و کارشناسان برابری فرصت‌های شغلی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی به استثنای خدمات قمار | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و متصدیان مسافری | کارمندان و دستیاران منابع انسانی به استثنای حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان روابط کار | تحلیل‌گران مدیریت و فرایند | کارمندان امور حقوق، دستمزد و ثبت ساعات کار | کارشناسان مدیریت پروژه | مدیران خدمات اجتماعی و عام‌المنفعه | مدیران آموزش و توسعه | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | کارشناسان مدیریت پروژه | مدیران خدمات اجتماعی و خدمات مردمی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان‌های خارجی | تولید محصولات غذایی و کشاورزی | ریاضیات | پرسنلی و منابع انسانی | تولید و فراوری | حقوق و مقررات دولتی</t>
+          <t>زبان خارجی | تولید مواد غذایی | ریاضیات | پرسنل و منابع انسانی | تولید و فرآوری | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بازرسان محصولات و امور کشاورزی | خریداران و مأموران خرید محصولات کشاورزی | مدیران پروژه ساختمانی و عمرانی | مروجان و آموزش‌دهندگان مدیریت مزرعه و اقتصاد خانواده | کشاورزان، دامداران و سایر مدیران بخش کشاورزی | کارگران مزارع، باغات و گلخانه‌ها | سرپرستان رده‌اول مشاغل ساختمانی و استخراج معدن | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی به استثنای خدمات قمار | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول کارکنان خدمات و نظافت اماکن | سرپرستان رده‌اول کارگران محوطه‌سازی و باغبانی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات جابه‌جایی بار و وسایل نقلیه | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول مهمانداران و متصدیان مسافری | سرپرستان رده‌اول کارکنان خدمات شخصی | سرپرستان رده‌اول کارگران خطوط تولید و عملیاتی | مدیران ارشد و مدیران عملیاتی | مدیران تولید صنعتی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | خریداران و کارشناسان خرید محصولات کشاورزی | مدیران پروژه‌های ساختمانی | کارشناسان ترویج و آموزش کشاورزی و اقتصاد خانواده | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | مدیران تولید صنعتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | درک مطلب | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | درک مطلب | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | زبان انگلیسی | حقوق و مقررات دولتی | مدیریت و امور اداری</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | ابتکار و اصالت | روانی کلام و ایده | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | اصالت | روانی ایده‌ها | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | داوران، میانجی‌گران و مصالحه‌گران حقوقی | مدیران عامل و ارشد اجرایی | مدیران حقوق، دستمزد و مزایا | کارشناسان حقوق، مزایا و طبقه‌بندی مشاغل | مدیران انطباق با مقررات | مصاحبه‌کنندگان و کارشناسان واجدین شرایط در برنامه‌های دولتی | نمایندگان و کارشناسان برابری فرصت‌های شغلی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان و دستیاران منابع انسانی به استثنای حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | وکلا | تحلیل‌گران مدیریت و فرایند | مدیران روابط عمومی | کارشناسان روابط عمومی | کارشناسان فروش خدمات به استثنای تبلیغات، بیمه، مالی و گردشگری | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>مدیران خدمات اداری و پشتیبانی | داوران، میانجی‌گران و صلح‌یاران | مدیران عامل و مدیران ارشد اجرایی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | وکلا | کارشناسان تحلیل مدیریت و روش‌ها | مدیران روابط عمومی | کارشناسان روابط عمومی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل و ترابری | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | ایمنی و امنیت عمومی | جغرافیا | فروش و بازاریابی | تولید و فراوری | آموزش و یادگیری | پرسنلی و منابع انسانی | حقوق و مقررات دولتی</t>
+          <t>حمل و نقل | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | ایمنی و امنیت عمومی | جغرافیا | فروش و بازاریابی | تولید و فرآوری | آموزش و پرورش | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | دید نزدیک | ابتکار و اصالت | روانی کلام و ایده | مهارت کار با اعداد | انعطاف‌پذیری در دسته‌بندی | تجسم فضایی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | اصالت | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان بار و حمل‌ونقل کالا | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات جابه‌جایی بار و وسایل نقلیه | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | مدیران ارشد و مدیران عملیاتی | مدیران تولید صنعتی | مدیران پروژه فناوری اطلاعات | تحلیل‌گران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت و فرایند | کارمندان تدارکات و کارپردازی | کارمندان برنامه‌ریزی تولید و تدارکات | کارشناسان مدیریت پروژه | مأموران خرید سایر حوزه‌ها | مدیران تدارکات و خرید | هماهنگ‌کنندگان بازیافت | مدیران فروش | توسعه‌دهندگان نرم‌افزار | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارگزاران حمل‌ونقل و بار | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | مدیران کل و مدیران عملیات | مدیران تولید صنعتی | مدیران پروژه‌های فناوری اطلاعات | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | هماهنگ‌کنندگان امور بازیافت | مدیران فروش | توسعه‌دهندگان نرم‌افزار | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نگارش | یادگیری فعال | شنیدن فعال | درک مطلب | ریاضیات | سخن گفتن | تفکر انتقادی | نظارت | استراتژی‌های یادگیری</t>
+          <t>نگارش | یادگیری فعال | گوش دادن فعال | درک مطلب | ریاضیات | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | حمل‌ونقل و ترابری | تولید و فراوری | رایانه و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | مدیریت و امور اداری | طراحی | آموزش و یادگیری | خدمات مشتریان و خدمات فردی</t>
+          <t>مهندسی و فناوری | ریاضیات | حمل و نقل | تولید و فرآوری | رایانه و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | مدیریت و اداره | طراحی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال ریاضی | بیان کتبی | روانی کلام و ایده | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | بیان شفاهی | ابتکار و اصالت | دید نزدیک | وضوح گفتار | مهارت کار با اعداد | انعطاف‌پذیری در دسته‌بندی | تشخیص گفتار | انعطاف‌پذیری بستار | تجسم فضایی | دید دور | توجه انتخابی</t>
+          <t>درک کتبی | استدلال ریاضی | بیان کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | اصالت | بینایی نزدیک | وضوح گفتار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | انعطاف‌پذیری بستار | تجسم | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان خودرو | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان و معماران سیستم‌های رایانه‌ای | کارشناسان برآورد هزینه و مترورها | مهندسان الکترونیک به استثنای رایانه | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک | تحلیل‌گران لجستیک | مهندسان تولید و ساخت | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه | مهندسان فروش فنی | توسعه‌دهندگان نرم‌افزار | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران فنی و مهندسی و معماری | مهندسان خودرو | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان و معماران سامانه‌های رایانه‌ای | کارشناسان برآورد هزینه و مترورها | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه | مهندسان فروش | توسعه‌دهندگان نرم‌افزار | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | حمل‌ونقل و ترابری | ریاضیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و یادگیری | جغرافیا | امور اداری و دفتری | تولید و فراوری | حقوق و مقررات دولتی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | حمل و نقل | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | جغرافیا | اداری | تولید و فرآوری | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | وضوح گفتار | مهارت کار با اعداد | انعطاف‌پذیری بستار | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | بیان کتبی | ابتکار و اصالت | روانی کلام و ایده | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | وضوح گفتار | توانایی عددی | انعطاف‌پذیری بستار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | اصالت | روانی ایده‌ها | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>طراحان و برنامه‌ریزان تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | متصدیان بار و حمل‌ونقل کالا | تحلیل‌گران سیستم‌های رایانه‌ای | متخصصان پایگاه داده و انبار داده | سرپرستان رده‌اول اپراتورهای ماشین‌آلات جابه‌جایی بار و وسایل نقلیه | متصدیان ارسال و خدمات فورواردری کالا | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت و فرایند | کارمندان تدارکات و کارپردازی | کارمندان برنامه‌ریزی تولید و تدارکات | کارشناسان مدیریت پروژه | مأموران خرید سایر حوزه‌ها | مدیران تدارکات و خرید | کارمندان انبارداری، دریافت و ارسال کالا | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | کارگزاران حمل‌ونقل و بار | تحلیل‌گران سیستم‌های کامپیوتری | متخصصان انباره داده | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارمندان انبار، ارسال و دریافت کالا | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | اقتصاد و حسابداری | ریاضیات | پرسنلی و منابع انسانی | مهندسی و فناوری | آموزش و یادگیری</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | اقتصاد و حسابداری | ریاضیات | پرسنل و منابع انسانی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی کلام و ایده | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم فضایی | به خاطرسپاری | استدلال ریاضی | مهارت کار با اعداد | سرعت ادراک | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | مدیران معماری و مهندسی | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و فناوری اطلاعات | مدیران پروژه ساختمانی و عمرانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران ارشد و مدیران عملیاتی | مهندسان صنایع | مدیران پروژه فناوری اطلاعات | کارشناسان لجستیک | تحلیل‌گران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت و فرایند | مدیران علوم طبیعی و پایه | تحلیل‌گران تحقیق در عملیات | کارمندان برنامه‌ریزی تولید و تدارکات | توسعه‌دهندگان نرم‌افزار | مدیران نصب تأسیسات انرژی خورشیدی | مدیران آموزش و توسعه</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران فنی و مهندسی و معماری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پروژه‌های ساختمانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران کل و مدیران عملیات | مهندسان صنایع | مدیران پروژه‌های فناوری اطلاعات | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | مدیران علوم طبیعی و پایه‌ای | تحلیل‌گران تحقیق در عملیات | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | توسعه‌دهندگان نرم‌افزار | مدیران اجرای پروژه‌های انرژی خورشیدی | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
